--- a/data/trans_orig/P79A4_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A4_2023-Clase-trans_orig.xlsx
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1626</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>72,82%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3143</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>49,63%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2082,7 +2082,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
